--- a/IA_generativa/Clase 2/Clase 2. embeddings.xlsx
+++ b/IA_generativa/Clase 2/Clase 2. embeddings.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francomansilla/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francomansilla/Library/CloudStorage/GoogleDrive-franco.andres.mansilla@gmail.com/Mi unidad/universidad mayor/Certificación 2/3. IA Generativa/Clases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CDF8F6-D479-1642-8D63-C9A270C9E413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F71C2F-56FF-6445-88A8-DC36C12B1953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33720" yWindow="600" windowWidth="33720" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33720" yWindow="600" windowWidth="33720" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
-    <sheet name="1. Rasgos manuales" sheetId="2" r:id="rId2"/>
-    <sheet name="2. Corpus" sheetId="3" r:id="rId3"/>
-    <sheet name="3. Coocurrencia" sheetId="4" r:id="rId4"/>
-    <sheet name="4. Qué mejorar" sheetId="5" r:id="rId5"/>
+    <sheet name="Instrucciones" sheetId="2" r:id="rId1"/>
+    <sheet name="1. Rasgos manuales" sheetId="3" r:id="rId2"/>
+    <sheet name="2. Corpus" sheetId="4" r:id="rId3"/>
+    <sheet name="3. Coocurrencia" sheetId="5" r:id="rId4"/>
+    <sheet name="4. Qué mejorar" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="v_auto">'1. Rasgos manuales'!$B$7:$G$7</definedName>
@@ -46,7 +46,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="101">
+  <si>
+    <t>Cómo construir un modelo de embeddings en Excel — perro, gato, conejo y auto</t>
+  </si>
   <si>
     <t>Un embedding es solo una lista de números que representa una palabra. Aquí vas a construir dos versiones con la misma idea de fondo: medir qué tan "cerca" están dos palabras comparando sus vectores. Se agregó un cuarto elemento, "auto", que no tiene nada que ver con los animales, para comprobar que el modelo lo nota — y para ver qué pasa cuando no lo nota.</t>
   </si>
@@ -75,12 +78,6 @@
     <t>Un resumen honesto de qué se simplificó en este ejercicio y cómo lo resuelven los modelos de embeddings reales — los mismos que usan ChatGPT, Gemini y Claude.</t>
   </si>
   <si>
-    <t>En las hojas 1 y 3 hay, al final, una matriz de similitud (coseno) entre las cuatro palabras. Edita los puntajes de la Hoja 1 o agrega oraciones a la Hoja 2, y mira cómo cambia el resultado.</t>
-  </si>
-  <si>
-    <t>Opción A · Rasgos elegidos a mano (rápido, pero subjetivo)</t>
-  </si>
-  <si>
     <t>Palabra</t>
   </si>
   <si>
@@ -129,7 +126,7 @@
     <t>Matriz de similitud (coseno) — 1 = idénticos, 0 = nada en común</t>
   </si>
   <si>
-    <t>Corpus: oraciones de ejemplo (hacen de "datos de entrenamiento")</t>
+    <t>Ojo con valor abosluto sobre un valor vs vector</t>
   </si>
   <si>
     <t>#</t>
@@ -228,9 +225,6 @@
     <t>Estaciono el auto en el garaje todas las noches.</t>
   </si>
   <si>
-    <t>El vector de cada palabra = cuántas veces aparece junto a cada palabra de contexto</t>
-  </si>
-  <si>
     <t>mascota</t>
   </si>
   <si>
@@ -291,9 +285,6 @@
     <t>garaje</t>
   </si>
   <si>
-    <t>Cada número de arriba salió contando coincidencias en el corpus — nadie lo eligió a mano. Las cinco últimas columnas (gasolina, maneja, ruedas, motor, garaje) solo existen para que "auto" tenga su propio contexto, igual que el resto.</t>
-  </si>
-  <si>
     <t>Misma fórmula que en la Hoja 1: similitud(A, B) = (A · B) / (|A| × |B|) — revisa esa hoja para la explicación completa de cada parte.</t>
   </si>
   <si>
@@ -351,17 +342,84 @@
     <t>Los vectores se ajustan millones de veces con descenso de gradiente, optimizando qué tan bien predicen el contexto real.</t>
   </si>
   <si>
-    <t>Cómo construir un modelo de embeddings en Excel — perro, gato, conejo y auto</t>
-  </si>
-  <si>
-    <t>Ojo con valor abosluto sobre un valor vs vector</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Opcion B |</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> El vector de cada palabra = cuántas veces aparece junto a cada palabra de contexto</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Corpus:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> oraciones de ejemplo (hacen de "datos de entrenamiento")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Opción A |</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rasgos elegidos a mano (rápido, pero subjetivo)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,22 +428,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
@@ -393,6 +440,7 @@
       <color rgb="FF6B6452"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -400,42 +448,122 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF6B6452"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF6B6452"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
-      <color rgb="FF3E7C6F"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,14 +572,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3E7C6F"/>
-        <bgColor rgb="FF6B6452"/>
+        <fgColor rgb="FFF4EFE3"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4EFE3"/>
-        <bgColor rgb="FFECE3CF"/>
+        <fgColor rgb="FF002060"/>
+        <bgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -482,87 +616,95 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +715,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -585,16 +727,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFD6C9A0"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF4EFE3"/>
-      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -605,27 +747,27 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFECE3CF"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FFD6C9A0"/>
+      <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF6B6452"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF3E7C6F"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF1F497D"/>
       <rgbColor rgb="FF333333"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
@@ -653,43 +795,42 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>190499</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>208643</xdr:rowOff>
+      <xdr:colOff>190440</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>18360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>560613</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
+      <xdr:colOff>560160</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>217431</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{903E7475-2504-32F0-3944-FDAFBCB42A88}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
+        <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="190499" y="5098143"/>
-          <a:ext cx="7772400" cy="3886200"/>
+          <a:off x="190440" y="5085720"/>
+          <a:ext cx="7230240" cy="3872880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -875,67 +1016,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="1" max="1" width="100" style="5" customWidth="1"/>
+    <col min="2" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="1" spans="1:3" s="9" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="3" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="6" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="9" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="12" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="17" spans="1:1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -944,274 +1086,279 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="24.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="24.33203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="24.33203125" style="9"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="20">
+        <v>7</v>
+      </c>
+      <c r="C4" s="20">
+        <v>8</v>
+      </c>
+      <c r="D4" s="20">
+        <v>9</v>
+      </c>
+      <c r="E4" s="20">
+        <v>1</v>
+      </c>
+      <c r="F4" s="20">
+        <v>3</v>
+      </c>
+      <c r="G4" s="20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="B5" s="20">
+        <v>4</v>
+      </c>
+      <c r="C5" s="20">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20">
+        <v>2</v>
+      </c>
+      <c r="E5" s="20">
+        <v>1</v>
+      </c>
+      <c r="F5" s="20">
         <v>8</v>
       </c>
-      <c r="D4" s="7">
-        <v>9</v>
-      </c>
-      <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="G5" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="20">
         <v>3</v>
       </c>
-      <c r="G4" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="C6" s="20">
+        <v>1</v>
+      </c>
+      <c r="D6" s="20">
+        <v>2</v>
+      </c>
+      <c r="E6" s="20">
+        <v>8</v>
+      </c>
+      <c r="F6" s="20">
+        <v>5</v>
+      </c>
+      <c r="G6" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="20">
+        <v>10</v>
+      </c>
+      <c r="C7" s="20">
+        <v>10</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="62" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+    </row>
+    <row r="13" spans="1:7" ht="43" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
-        <v>4</v>
-      </c>
-      <c r="C5" s="7">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7">
-        <v>2</v>
-      </c>
-      <c r="E5" s="7">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7">
-        <v>8</v>
-      </c>
-      <c r="G5" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="E16" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7">
-        <v>3</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7">
-        <v>2</v>
-      </c>
-      <c r="E6" s="7">
-        <v>8</v>
-      </c>
-      <c r="F6" s="7">
-        <v>5</v>
-      </c>
-      <c r="G6" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="7">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7">
-        <v>10</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-    </row>
-    <row r="13" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="11">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="23">
         <f>SUMPRODUCT($B$4:$G$4,$B$4:$G$4)/(SQRT(SUMSQ($B$4:$G$4))*SQRT(SUMSQ($B$4:$G$4)))</f>
         <v>0.99999999999999978</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="23">
         <f>SUMPRODUCT($B$4:$G$4,$B$5:$G$5)/(SQRT(SUMSQ($B$4:$G$4))*SQRT(SUMSQ($B$5:$G$5)))</f>
         <v>0.78100535712894092</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="23">
         <f>SUMPRODUCT($B$4:$G$4,$B$6:$G$6)/(SQRT(SUMSQ($B$4:$G$4))*SQRT(SUMSQ($B$6:$G$6)))</f>
         <v>0.62300546317328442</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="23">
         <f>SUMPRODUCT($B$4:$G$4,$B$7:$G$7)/(SQRT(SUMSQ($B$4:$G$4))*SQRT(SUMSQ($B$7:$G$7)))</f>
         <v>0.62828086243754322</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="11">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="23">
         <f>SUMPRODUCT($B$5:$G$5,$B$4:$G$4)/(SQRT(SUMSQ($B$5:$G$5))*SQRT(SUMSQ($B$4:$G$4)))</f>
         <v>0.78100535712894092</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="23">
         <f>SUMPRODUCT($B$5:$G$5,$B$5:$G$5)/(SQRT(SUMSQ($B$5:$G$5))*SQRT(SUMSQ($B$5:$G$5)))</f>
         <v>1</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="23">
         <f>SUMPRODUCT($B$5:$G$5,$B$6:$G$6)/(SQRT(SUMSQ($B$5:$G$5))*SQRT(SUMSQ($B$6:$G$6)))</f>
         <v>0.74051422062728756</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="23">
         <f>SUMPRODUCT($B$5:$G$5,$B$7:$G$7)/(SQRT(SUMSQ($B$5:$G$5))*SQRT(SUMSQ($B$7:$G$7)))</f>
         <v>0.50395263067896967</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="11">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="23">
         <f>SUMPRODUCT($B$6:$G$6,$B$4:$G$4)/(SQRT(SUMSQ($B$6:$G$6))*SQRT(SUMSQ($B$4:$G$4)))</f>
         <v>0.62300546317328442</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="23">
         <f>SUMPRODUCT($B$6:$G$6,$B$5:$G$5)/(SQRT(SUMSQ($B$6:$G$6))*SQRT(SUMSQ($B$5:$G$5)))</f>
         <v>0.74051422062728756</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="23">
         <f>SUMPRODUCT($B$6:$G$6,$B$6:$G$6)/(SQRT(SUMSQ($B$6:$G$6))*SQRT(SUMSQ($B$6:$G$6)))</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="23">
         <f>SUMPRODUCT($B$6:$G$6,$B$7:$G$7)/(SQRT(SUMSQ($B$6:$G$6))*SQRT(SUMSQ($B$7:$G$7)))</f>
         <v>0.23990405756162689</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="11">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="23">
         <f>SUMPRODUCT($B$7:$G$7,$B$4:$G$4)/(SQRT(SUMSQ($B$7:$G$7))*SQRT(SUMSQ($B$4:$G$4)))</f>
         <v>0.62828086243754322</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="23">
         <f>SUMPRODUCT($B$7:$G$7,$B$5:$G$5)/(SQRT(SUMSQ($B$7:$G$7))*SQRT(SUMSQ($B$5:$G$5)))</f>
         <v>0.50395263067896967</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="23">
         <f>SUMPRODUCT($B$7:$G$7,$B$6:$G$6)/(SQRT(SUMSQ($B$7:$G$7))*SQRT(SUMSQ($B$6:$G$6)))</f>
         <v>0.23990405756162689</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="23">
         <f>SUMPRODUCT($B$7:$G$7,$B$7:$G$7)/(SQRT(SUMSQ($B$7:$G$7))*SQRT(SUMSQ($B$7:$G$7)))</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B22" s="31"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1225,265 +1372,268 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="1" max="1" width="6" style="5" customWidth="1"/>
+    <col min="2" max="2" width="70" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" s="9" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="B3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
-        <v>1</v>
-      </c>
-      <c r="B4" s="13" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="15">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
-        <v>2</v>
-      </c>
-      <c r="B5" s="13" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
-        <v>3</v>
-      </c>
-      <c r="B6" s="13" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="15">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
-        <v>4</v>
-      </c>
-      <c r="B7" s="13" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="15">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="12">
-        <v>5</v>
-      </c>
-      <c r="B8" s="13" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="15">
+        <v>6</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
-        <v>6</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="15">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
-        <v>7</v>
-      </c>
-      <c r="B10" s="13" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="15">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="12">
-        <v>8</v>
-      </c>
-      <c r="B11" s="13" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="15">
+        <v>9</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
-        <v>9</v>
-      </c>
-      <c r="B12" s="13" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="15">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="12">
-        <v>10</v>
-      </c>
-      <c r="B13" s="13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="15">
+        <v>11</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="12">
-        <v>11</v>
-      </c>
-      <c r="B14" s="13" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="15">
+        <v>12</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="12">
-        <v>12</v>
-      </c>
-      <c r="B15" s="13" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="15">
+        <v>13</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="12">
-        <v>13</v>
-      </c>
-      <c r="B16" s="13" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="15">
+        <v>14</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="12">
-        <v>14</v>
-      </c>
-      <c r="B17" s="13" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="15">
+        <v>15</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="12">
-        <v>15</v>
-      </c>
-      <c r="B18" s="13" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="15">
+        <v>16</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="12">
-        <v>16</v>
-      </c>
-      <c r="B19" s="13" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="15">
+        <v>17</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="12">
-        <v>17</v>
-      </c>
-      <c r="B20" s="13" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="15">
+        <v>18</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="12">
-        <v>18</v>
-      </c>
-      <c r="B21" s="13" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="15">
+        <v>19</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="12">
-        <v>19</v>
-      </c>
-      <c r="B22" s="13" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="15">
+        <v>20</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="12">
-        <v>20</v>
-      </c>
-      <c r="B23" s="13" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="15">
+        <v>21</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="12">
-        <v>21</v>
-      </c>
-      <c r="B24" s="13" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="15">
+        <v>22</v>
+      </c>
+      <c r="B25" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="12">
-        <v>22</v>
-      </c>
-      <c r="B25" s="13" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="15">
+        <v>23</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="12">
-        <v>23</v>
-      </c>
-      <c r="B26" s="13" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="15">
+        <v>24</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="12">
-        <v>24</v>
-      </c>
-      <c r="B27" s="13" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="15">
+        <v>25</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="12">
-        <v>25</v>
-      </c>
-      <c r="B28" s="13" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="15">
+        <v>26</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="12">
-        <v>26</v>
-      </c>
-      <c r="B29" s="13" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="15">
+        <v>27</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="12">
-        <v>27</v>
-      </c>
-      <c r="B30" s="13" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="15">
+        <v>28</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="12">
-        <v>28</v>
-      </c>
-      <c r="B31" s="13" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="15">
+        <v>29</v>
+      </c>
+      <c r="B32" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="12">
-        <v>29</v>
-      </c>
-      <c r="B32" s="13" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="15">
+        <v>30</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="12">
-        <v>30</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1493,562 +1643,539 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="20" customWidth="1"/>
-    <col min="2" max="21" width="12" style="20" customWidth="1"/>
-    <col min="22" max="16384" width="8.6640625" style="20"/>
+    <col min="1" max="1" width="10" style="27" customWidth="1"/>
+    <col min="2" max="21" width="12" style="27" customWidth="1"/>
+    <col min="22" max="16384" width="8.6640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:21" s="9" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="3" spans="1:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="D3" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="E3" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="F3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="G3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="H3" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="I3" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="J3" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="K3" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="L3" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="M3" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="N3" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="O3" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="P3" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="Q3" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="R3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="S3" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="T3" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="U3" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="T3" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" s="17" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(B$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="C4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(C$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(D$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(E$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(F$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(G$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(H$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(I$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="J4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(J$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(K$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(L$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(M$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(N$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(O$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(P$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(Q$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(R$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(S$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(T$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(U$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(B$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="C4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(C$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="D4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(D$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="E4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(E$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(F$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(G$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="H4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(H$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="I4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(I$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(J$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(K$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(L$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(M$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(N$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="O4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(O$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(P$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(Q$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="R4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(R$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="S4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(S$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(T$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A4,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(U$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
+      <c r="B5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(B$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(C$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(D$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(E$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(F$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="G5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(G$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(H$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(I$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(J$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(K$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="L5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(L$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(M$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(N$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(O$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(P$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(Q$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(R$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(S$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(T$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="31">
+        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(U$3,'2. Corpus'!$B$4:$B$33)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(B$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="C5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(C$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="D5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(D$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="E5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(E$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(F$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="G5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(G$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(H$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(I$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(J$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="K5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(K$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="L5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(L$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(M$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(N$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(O$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="P5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(P$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(Q$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(R$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="S5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(S$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="T5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(T$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-      <c r="U5" s="22">
-        <f>SUMPRODUCT(ISNUMBER(SEARCH($A5,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(U$3,'2. Corpus'!$B$4:$B$33)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="B6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(B$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(C$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(D$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(E$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(F$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(G$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(H$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(I$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(J$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(K$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(L$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(M$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>2</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(N$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(O$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(P$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(Q$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="R6" s="22">
+      <c r="R6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(R$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="S6" s="22">
+      <c r="S6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(S$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="T6" s="22">
+      <c r="T6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(T$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="U6" s="22">
+      <c r="U6" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A6,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(U$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="22">
+      <c r="A7" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(B$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(C$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(D$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(E$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(F$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(G$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(H$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(I$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(J$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(K$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="L7" s="22">
+      <c r="L7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(L$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(M$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="N7" s="22">
+      <c r="N7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(N$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(O$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(P$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="22">
+      <c r="Q7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(Q$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="R7" s="22">
+      <c r="R7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(R$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="S7" s="22">
+      <c r="S7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(S$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="T7" s="22">
+      <c r="T7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(T$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
-      <c r="U7" s="22">
+      <c r="U7" s="31">
         <f>SUMPRODUCT(ISNUMBER(SEARCH($A7,'2. Corpus'!$B$4:$B$33))*ISNUMBER(SEARCH(U$3,'2. Corpus'!$B$4:$B$33)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-    </row>
-    <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
-        <v>82</v>
+    <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="29" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="26" t="s">
-        <v>83</v>
+      <c r="A12" s="33"/>
+      <c r="B12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="27">
+      <c r="A13" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="30">
         <f>SUMPRODUCT($B$4:$U$4,$B$4:$U$4)/(SQRT(SUMSQ($B$4:$U$4))*SQRT(SUMSQ($B$4:$U$4)))</f>
         <v>0.99999999999999978</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C13" s="30">
         <f>SUMPRODUCT($B$4:$U$4,$B$5:$U$5)/(SQRT(SUMSQ($B$4:$U$4))*SQRT(SUMSQ($B$5:$U$5)))</f>
         <v>0.62499999999999989</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D13" s="30">
         <f>SUMPRODUCT($B$4:$U$4,$B$6:$U$6)/(SQRT(SUMSQ($B$4:$U$4))*SQRT(SUMSQ($B$6:$U$6)))</f>
         <v>0.42640143271122083</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E13" s="30">
         <f>SUMPRODUCT($B$4:$U$4,$B$7:$U$7)/(SQRT(SUMSQ($B$4:$U$4))*SQRT(SUMSQ($B$7:$U$7)))</f>
         <v>0.14433756729740646</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="27">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="30">
         <f>SUMPRODUCT($B$5:$U$5,$B$4:$U$4)/(SQRT(SUMSQ($B$5:$U$5))*SQRT(SUMSQ($B$4:$U$4)))</f>
         <v>0.62499999999999989</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C14" s="30">
         <f>SUMPRODUCT($B$5:$U$5,$B$5:$U$5)/(SQRT(SUMSQ($B$5:$U$5))*SQRT(SUMSQ($B$5:$U$5)))</f>
         <v>0.99999999999999978</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D14" s="30">
         <f>SUMPRODUCT($B$5:$U$5,$B$6:$U$6)/(SQRT(SUMSQ($B$5:$U$5))*SQRT(SUMSQ($B$6:$U$6)))</f>
         <v>0.42640143271122083</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E14" s="30">
         <f>SUMPRODUCT($B$5:$U$5,$B$7:$U$7)/(SQRT(SUMSQ($B$5:$U$5))*SQRT(SUMSQ($B$7:$U$7)))</f>
         <v>0.14433756729740646</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="27">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="30">
         <f>SUMPRODUCT($B$6:$U$6,$B$4:$U$4)/(SQRT(SUMSQ($B$6:$U$6))*SQRT(SUMSQ($B$4:$U$4)))</f>
         <v>0.42640143271122083</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C15" s="30">
         <f>SUMPRODUCT($B$6:$U$6,$B$5:$U$5)/(SQRT(SUMSQ($B$6:$U$6))*SQRT(SUMSQ($B$5:$U$5)))</f>
         <v>0.42640143271122083</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D15" s="30">
         <f>SUMPRODUCT($B$6:$U$6,$B$6:$U$6)/(SQRT(SUMSQ($B$6:$U$6))*SQRT(SUMSQ($B$6:$U$6)))</f>
         <v>1</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E15" s="30">
         <f>SUMPRODUCT($B$6:$U$6,$B$7:$U$7)/(SQRT(SUMSQ($B$6:$U$6))*SQRT(SUMSQ($B$7:$U$7)))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="27">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30">
         <f>SUMPRODUCT($B$7:$U$7,$B$4:$U$4)/(SQRT(SUMSQ($B$7:$U$7))*SQRT(SUMSQ($B$4:$U$4)))</f>
         <v>0.14433756729740646</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C16" s="30">
         <f>SUMPRODUCT($B$7:$U$7,$B$5:$U$5)/(SQRT(SUMSQ($B$7:$U$7))*SQRT(SUMSQ($B$5:$U$5)))</f>
         <v>0.14433756729740646</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D16" s="30">
         <f>SUMPRODUCT($B$7:$U$7,$B$6:$U$6)/(SQRT(SUMSQ($B$7:$U$7))*SQRT(SUMSQ($B$6:$U$6)))</f>
         <v>0</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E16" s="30">
         <f>SUMPRODUCT($B$7:$U$7,$B$7:$U$7)/(SQRT(SUMSQ($B$7:$U$7))*SQRT(SUMSQ($B$7:$U$7)))</f>
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="23" t="s">
-        <v>84</v>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="28" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2058,82 +2185,84 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" s="9" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+    <row r="6" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="C7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="14" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="C8" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="14" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="C9" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="14" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+      <c r="C10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="14" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="C11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+    </row>
+    <row r="13" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
